--- a/synthetic_work_orders_sample.xlsx
+++ b/synthetic_work_orders_sample.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,91 +425,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Work Order Number</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Closed On</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Project Status</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>System Status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Work Order Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Billing Account</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Address Name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Address 1</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Address 2</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Address 3</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>State Or Province</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Postal Code</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Assigned To Resource</t>
         </is>
@@ -905,12 +917,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T2001102</t>
+          <t>T2001111</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-14 08:06:00</t>
+          <t>2026-04-14 08:13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -930,7 +942,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>WATERFRONT BACKHAUL POINT INSPECTION (DRW-WF1)</t>
+          <t>METRO LINK AGGREGATION NODE RECORD REVIEW (ADL-LNK2)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -940,7 +952,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>WATERFRONT BACKHAUL POINT</t>
+          <t>METRO LINK AGGREGATION NODE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -951,29 +963,25 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-12.4634</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>130.8456</t>
-        </is>
-      </c>
+          <t>-34.9285</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Resource Team B</t>
+          <t>Resource Team D</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T2001106</t>
+          <t>T2001102</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-14 08:12:00</t>
+          <t>2026-04-14 08:06:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,57 +1001,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ST GEORGES TERRACE FEEDER HUB ALIGNMENT (PER-CITY4)</t>
+          <t>WATERFRONT BACKHAUL POINT INSPECTION (DRW-WF1)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NEC AUSTRALIA LTD WA</t>
+          <t>TELSTRA CORPORATION LTD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ST GEORGES TERRACE FEEDER HUB</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>250 St Georges Terrace</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Riser Closet 2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>(PER-CITY4)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>PERTH</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
+          <t>WATERFRONT BACKHAUL POINT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>bad-lat</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1055,12 +1039,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T2001103</t>
+          <t>T2001106</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-14 08:07:00</t>
+          <t>2026-04-14 08:12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,71 +1059,79 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>INSTALL</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GEORGE STREET CORRIDOR SWITCH REFRESH (SYD-CBD5)</t>
+          <t>ST GEORGES TERRACE FEEDER HUB ALIGNMENT (PER-CITY4)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TELSTRA CORPORATION LTD</t>
+          <t>NEC AUSTRALIA LTD WA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>GEORGE STREET CORRIDOR SWITCH</t>
+          <t>ST GEORGES TERRACE FEEDER HUB</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>41 George Street</t>
+          <t>250 St Georges Terrace</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Roof Access Communications Rack</t>
+          <t>Riser Closet 2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>(SYD-CBD5)</t>
+          <t>(PER-CITY4)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>THE ROCKS</t>
+          <t>PERTH</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NSW</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>bad-lat</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Resource Team A</t>
+          <t>Resource Team B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T2001109</t>
+          <t>T2001112</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04-14 08:18:00</t>
+          <t>2026-04-14 08:19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1159,7 +1151,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RUNDLE MALL DISTRIBUTION RACK CLEANUP (ADL-MALL1)</t>
+          <t>PLACEHOLDER ADDRESS ENTRY FOR DATA QA WORKFLOW</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1169,64 +1161,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RUNDLE MALL DISTRIBUTION RACK</t>
+          <t>PLACEHOLDER SITE ENTRY</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18 Rundle Mall</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Switch Room South</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>(ADL-MALL1)</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ADELAIDE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>51.5074</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-0.1278</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Resource Team B</t>
+          <t>Resource Team A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T2001110</t>
+          <t>T2001103</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-04-14 08:20:00</t>
+          <t>2026-04-14 08:07:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1241,12 +1225,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>INSTALL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PENDING SITE DETAILS - MANUAL REVIEW REQUIRED</t>
+          <t>GEORGE STREET CORRIDOR SWITCH REFRESH (SYD-CBD5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1256,38 +1240,204 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>UNASSIGNED SITE RECORD</t>
+          <t>GEORGE STREET CORRIDOR SWITCH</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>   </t>
+          <t>41 George Street</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>Roof Access Communications Rack</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>(SYD-CBD5)</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t> </t>
+          <t>THE ROCKS</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t> </t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
+        <is>
+          <t>Resource Team A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T2001109</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:18:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Final Completion</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed - Posted</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INSTALL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RUNDLE MALL DISTRIBUTION RACK CLEANUP (ADL-MALL1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TELSTRA CORPORATION LTD</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>RUNDLE MALL DISTRIBUTION RACK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>18 Rundle Mall</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Switch Room South</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>(ADL-MALL1)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ADELAIDE</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>51.5074</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>-0.1278</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Resource Team B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T2001110</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:20:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Final Completion</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed - Posted</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PENDING SITE DETAILS - MANUAL REVIEW REQUIRED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TELSTRA CORPORATION LTD</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>UNASSIGNED SITE RECORD</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>   </t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Resource Team A</t>
         </is>
